--- a/topic_1_img/topic_1_sol.xlsx
+++ b/topic_1_img/topic_1_sol.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Data/Github/lecture_financial_statements_analysis/topic_1_img/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733C8FC2-79B8-054F-A7CA-3664F819ABC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62BA121-3FE5-E747-AC2C-5063494232E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20840" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="2040" windowWidth="38400" windowHeight="19200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_transactions" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,6 @@
     <t>#</t>
   </si>
   <si>
-    <t>Fixed Assets</t>
-  </si>
-  <si>
     <t>=</t>
   </si>
   <si>
@@ -417,6 +414,9 @@
   </si>
   <si>
     <t>Current Assets</t>
+  </si>
+  <si>
+    <t>Noncurrent Assets</t>
   </si>
 </sst>
 </file>
@@ -1015,6 +1015,9 @@
     <xf numFmtId="9" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1031,9 +1034,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2078,83 +2078,83 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="111" t="s">
+      <c r="D3" s="112" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="113" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="112" t="s">
+      <c r="I3" s="113"/>
+      <c r="J3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="112"/>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="113" t="s">
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="114" t="s">
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
+      <c r="T3" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="114"/>
-      <c r="T3" s="6" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="15" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="N4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="O4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="T4" s="6"/>
     </row>
@@ -2171,7 +2171,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2259,7 +2259,7 @@
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" s="9">
         <v>500</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="9">
         <v>-500</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2345,7 +2345,7 @@
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -2364,7 +2364,7 @@
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B14" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="9">
         <v>-1600</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="11"/>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" s="9">
         <f t="shared" ref="K19:R19" si="2">SUM(K5:K18)</f>
@@ -2685,22 +2685,22 @@
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
-      <c r="D23" s="115" t="s">
+      <c r="D23" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="115" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="115"/>
-      <c r="L23" s="115"/>
-      <c r="M23" s="115"/>
-      <c r="N23" s="115"/>
-      <c r="O23" s="115"/>
+      <c r="K23" s="116"/>
+      <c r="L23" s="116"/>
+      <c r="M23" s="116"/>
+      <c r="N23" s="116"/>
+      <c r="O23" s="116"/>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
@@ -2734,7 +2734,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
@@ -2742,7 +2742,7 @@
       <c r="H25" s="20"/>
       <c r="I25" s="13"/>
       <c r="J25" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K25" s="19"/>
       <c r="L25" s="19"/>
@@ -2760,7 +2760,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
@@ -2792,7 +2792,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
@@ -2825,7 +2825,7 @@
       <c r="C28" s="13"/>
       <c r="D28" s="16"/>
       <c r="E28" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
@@ -2857,7 +2857,7 @@
       <c r="C29" s="13"/>
       <c r="D29" s="16"/>
       <c r="E29" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
@@ -2884,14 +2884,14 @@
       <c r="C30" s="13"/>
       <c r="D30" s="16"/>
       <c r="E30" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="H30" s="23"/>
       <c r="I30" s="13"/>
       <c r="J30" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
@@ -2913,7 +2913,7 @@
       <c r="C31" s="13"/>
       <c r="D31" s="16"/>
       <c r="E31" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
@@ -2921,7 +2921,7 @@
       <c r="I31" s="13"/>
       <c r="J31" s="16"/>
       <c r="K31" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
@@ -2945,7 +2945,7 @@
       <c r="I32" s="13"/>
       <c r="J32" s="16"/>
       <c r="K32" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L32" s="13"/>
       <c r="M32" s="13"/>
@@ -2965,7 +2965,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
@@ -2977,7 +2977,7 @@
       <c r="I33" s="13"/>
       <c r="J33" s="16"/>
       <c r="K33" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
@@ -2998,7 +2998,7 @@
       <c r="C34" s="13"/>
       <c r="D34" s="16"/>
       <c r="E34" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
@@ -3009,7 +3009,7 @@
       <c r="I34" s="13"/>
       <c r="J34" s="16"/>
       <c r="K34" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
@@ -3027,7 +3027,7 @@
       <c r="C35" s="13"/>
       <c r="D35" s="16"/>
       <c r="E35" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
@@ -3035,7 +3035,7 @@
       <c r="I35" s="13"/>
       <c r="J35" s="16"/>
       <c r="K35" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L35" s="13"/>
       <c r="M35" s="13"/>
@@ -3053,7 +3053,7 @@
       <c r="C36" s="13"/>
       <c r="D36" s="16"/>
       <c r="E36" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
@@ -3061,7 +3061,7 @@
       <c r="I36" s="13"/>
       <c r="J36" s="16"/>
       <c r="K36" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
@@ -3088,7 +3088,7 @@
       <c r="I37" s="13"/>
       <c r="J37" s="16"/>
       <c r="K37" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L37" s="13"/>
       <c r="M37" s="13"/>
@@ -3111,7 +3111,7 @@
       <c r="H38" s="23"/>
       <c r="I38" s="13"/>
       <c r="J38" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K38" s="13"/>
       <c r="L38" s="13"/>
@@ -3132,7 +3132,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E39" s="28"/>
       <c r="F39" s="28"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I39" s="13"/>
       <c r="J39" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K39" s="28"/>
       <c r="L39" s="28"/>
@@ -3164,7 +3164,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
@@ -3192,14 +3192,14 @@
       <c r="C41" s="13"/>
       <c r="D41" s="16"/>
       <c r="E41" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
       <c r="H41" s="23"/>
       <c r="I41" s="13"/>
       <c r="J41" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K41" s="13"/>
       <c r="L41" s="13"/>
@@ -3218,7 +3218,7 @@
       <c r="C42" s="13"/>
       <c r="D42" s="16"/>
       <c r="E42" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F42" s="13"/>
       <c r="G42" s="13"/>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K42" s="13"/>
       <c r="L42" s="13"/>
@@ -3250,14 +3250,14 @@
       <c r="C43" s="13"/>
       <c r="D43" s="16"/>
       <c r="E43" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
       <c r="H43" s="23"/>
       <c r="I43" s="13"/>
       <c r="J43" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K43" s="28"/>
       <c r="L43" s="28"/>
@@ -3279,7 +3279,7 @@
       <c r="C44" s="13"/>
       <c r="D44" s="16"/>
       <c r="E44" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>
@@ -3311,7 +3311,7 @@
       <c r="H45" s="23"/>
       <c r="I45" s="13"/>
       <c r="J45" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K45" s="13"/>
       <c r="L45" s="13"/>
@@ -3332,7 +3332,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
       <c r="D46" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="13"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="I46" s="13"/>
       <c r="J46" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K46" s="13"/>
       <c r="L46" s="13"/>
@@ -3362,7 +3362,7 @@
       <c r="C47" s="13"/>
       <c r="D47" s="16"/>
       <c r="E47" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="I47" s="13"/>
       <c r="J47" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K47" s="28"/>
       <c r="L47" s="28"/>
@@ -3394,7 +3394,7 @@
       <c r="C48" s="13"/>
       <c r="D48" s="16"/>
       <c r="E48" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
@@ -3418,7 +3418,7 @@
       <c r="C49" s="13"/>
       <c r="D49" s="16"/>
       <c r="E49" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
@@ -3463,7 +3463,7 @@
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E51" s="13"/>
       <c r="F51" s="13"/>
@@ -3491,7 +3491,7 @@
       <c r="C52" s="13"/>
       <c r="D52" s="16"/>
       <c r="E52" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
@@ -3518,7 +3518,7 @@
       <c r="C53" s="13"/>
       <c r="D53" s="16"/>
       <c r="E53" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
@@ -4272,15 +4272,15 @@
   <sheetData>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="35" t="s">
         <v>71</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B10" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="37">
         <v>3568</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="11" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="37">
         <v>788</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="12" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="37">
         <v>1279</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="13" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" s="37">
         <v>640</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B14" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" s="37">
         <v>900</v>
@@ -4325,7 +4325,7 @@
     </row>
     <row r="15" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="37">
         <v>2043</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="16" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B16" s="36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="37">
         <v>1939</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B17" s="36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" s="37">
         <v>1377</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B18" s="36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="37">
         <v>6025</v>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B19" s="36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" s="37">
         <v>4324</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B20" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C20" s="37">
         <v>259</v>
@@ -4385,17 +4385,17 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="117" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B28" s="116" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="116"/>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B29" s="42"/>
@@ -4406,18 +4406,18 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B30" s="45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="46"/>
       <c r="D30" s="46"/>
       <c r="E30" s="46"/>
       <c r="F30" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="B31" s="48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="43"/>
       <c r="D31" s="43"/>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="32" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="B32" s="50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="51"/>
@@ -4442,7 +4442,7 @@
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="42"/>
       <c r="C33" s="43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" s="43"/>
       <c r="E33" s="43"/>
@@ -4454,7 +4454,7 @@
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="42"/>
       <c r="C34" s="43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" s="43"/>
       <c r="E34" s="43"/>
@@ -4466,7 +4466,7 @@
     <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="42"/>
       <c r="C35" s="43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="43"/>
       <c r="E35" s="43"/>
@@ -4478,7 +4478,7 @@
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="42"/>
       <c r="C36" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" s="43"/>
       <c r="E36" s="43"/>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="38" spans="2:6" ht="15" x14ac:dyDescent="0.2">
       <c r="B38" s="50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="51"/>
       <c r="D38" s="51"/>
@@ -4506,7 +4506,7 @@
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="42"/>
       <c r="C39" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" s="43"/>
       <c r="E39" s="43"/>
@@ -4518,7 +4518,7 @@
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="42"/>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40" s="43"/>
       <c r="F40" s="53">
@@ -4529,7 +4529,7 @@
     <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="42"/>
       <c r="C41" s="43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" s="43"/>
       <c r="E41" s="43"/>
@@ -4538,7 +4538,7 @@
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D42" s="43"/>
       <c r="E42" s="43"/>
@@ -4547,7 +4547,7 @@
     <row r="43" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B43" s="42"/>
       <c r="C43" s="43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D43" s="43"/>
       <c r="E43" s="43"/>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="45" spans="2:6" ht="15" x14ac:dyDescent="0.2">
       <c r="B45" s="48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="54"/>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" s="43"/>
       <c r="D46" s="43"/>
@@ -4590,7 +4590,7 @@
     <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="42"/>
       <c r="C47" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D47" s="43"/>
       <c r="E47" s="43"/>
@@ -4602,7 +4602,7 @@
     <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="42"/>
       <c r="C48" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D48" s="43"/>
       <c r="E48" s="43"/>
@@ -4611,7 +4611,7 @@
     <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="42"/>
       <c r="C49" s="43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D49" s="43"/>
       <c r="E49" s="43"/>
@@ -4620,7 +4620,7 @@
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B50" s="42"/>
       <c r="C50" s="43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D50" s="43"/>
       <c r="E50" s="43"/>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" s="43"/>
       <c r="D52" s="43"/>
@@ -4648,7 +4648,7 @@
     <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="42"/>
       <c r="C53" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D53" s="43"/>
       <c r="E53" s="43"/>
@@ -4660,7 +4660,7 @@
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="42"/>
       <c r="C54" s="43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D54" s="43"/>
       <c r="E54" s="43"/>
@@ -4669,7 +4669,7 @@
     <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="42"/>
       <c r="C55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D55" s="43"/>
       <c r="E55" s="43"/>
@@ -4687,7 +4687,7 @@
     </row>
     <row r="57" spans="2:6" ht="15" x14ac:dyDescent="0.2">
       <c r="B57" s="55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C57" s="43"/>
       <c r="D57" s="43"/>
@@ -4700,7 +4700,7 @@
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="42"/>
       <c r="C58" s="43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="43"/>
       <c r="E58" s="43"/>
@@ -4712,7 +4712,7 @@
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="42"/>
       <c r="C59" s="43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D59" s="43"/>
       <c r="E59" s="43"/>
@@ -4754,15 +4754,15 @@
   <sheetData>
     <row r="7" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B7" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="57" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" s="58">
         <v>51692</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="9" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B9" s="57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C9" s="58">
         <v>71</v>
@@ -4778,7 +4778,7 @@
     </row>
     <row r="10" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B10" s="57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="58">
         <v>2714</v>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="11" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B11" s="57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="58">
         <v>72184</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B13" s="57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="58">
         <v>4294</v>
@@ -4808,7 +4808,7 @@
     </row>
     <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B14" s="57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="58">
         <v>1580</v>
@@ -4816,7 +4816,7 @@
     </row>
     <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B15" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="58">
         <v>16561</v>
@@ -4824,7 +4824,7 @@
     </row>
     <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B16" s="60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" s="61">
         <v>72618</v>
@@ -4832,18 +4832,18 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B21" s="116" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
+      <c r="B21" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="117"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B22" s="42"/>
@@ -4855,19 +4855,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B23" s="45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="46"/>
       <c r="E23" s="46"/>
       <c r="F23" s="46"/>
       <c r="G23" s="47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B24" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" s="43"/>
       <c r="D24" s="43"/>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="B25" s="42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" s="43"/>
       <c r="D25" s="43"/>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="B26" s="48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B28" s="42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="43"/>
       <c r="D28" s="43"/>
@@ -4927,7 +4927,7 @@
     </row>
     <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="B29" s="42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" s="43"/>
       <c r="D29" s="43"/>
@@ -4937,7 +4937,7 @@
     </row>
     <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="B30" s="48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C30" s="54"/>
       <c r="D30" s="54"/>
@@ -4958,7 +4958,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B32" s="42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="43"/>
       <c r="D32" s="43"/>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="43"/>
       <c r="D33" s="43"/>
@@ -4981,7 +4981,7 @@
     </row>
     <row r="34" spans="2:8" ht="15" x14ac:dyDescent="0.2">
       <c r="B34" s="48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" s="54"/>
       <c r="D34" s="54"/>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" s="43"/>
       <c r="D36" s="43"/>
@@ -5015,7 +5015,7 @@
     </row>
     <row r="37" spans="2:8" ht="15" x14ac:dyDescent="0.2">
       <c r="B37" s="42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C37" s="43"/>
       <c r="D37" s="43"/>
@@ -5028,7 +5028,7 @@
     </row>
     <row r="38" spans="2:8" ht="15" x14ac:dyDescent="0.2">
       <c r="B38" s="48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C38" s="54"/>
       <c r="D38" s="54"/>
@@ -5077,22 +5077,22 @@
   </cols>
   <sheetData>
     <row r="16" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="117" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17" s="69"/>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18" s="71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="72"/>
       <c r="D18" s="72"/>
@@ -5118,7 +5118,7 @@
       <c r="F18" s="73"/>
       <c r="G18" s="68"/>
       <c r="H18" s="71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" s="72"/>
       <c r="J18" s="72"/>
@@ -5128,7 +5128,7 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" s="74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="68"/>
       <c r="D19" s="68"/>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
@@ -5151,7 +5151,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20" s="77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="G20" s="68"/>
       <c r="H20" s="69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I20" s="68"/>
       <c r="J20" s="68"/>
@@ -5175,7 +5175,7 @@
     <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21" s="69"/>
       <c r="C21" s="68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="68"/>
       <c r="E21" s="68"/>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G21" s="68"/>
       <c r="H21" s="74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I21" s="81"/>
       <c r="J21" s="81"/>
@@ -5197,7 +5197,7 @@
     <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22" s="69"/>
       <c r="C22" s="68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" s="68"/>
       <c r="E22" s="68"/>
@@ -5215,14 +5215,14 @@
     <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B23" s="69"/>
       <c r="C23" s="68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="68"/>
       <c r="E23" s="68"/>
       <c r="F23" s="76"/>
       <c r="G23" s="68"/>
       <c r="H23" s="69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I23" s="68"/>
       <c r="J23" s="68"/>
@@ -5235,7 +5235,7 @@
     <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B24" s="69"/>
       <c r="C24" s="68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="68"/>
       <c r="E24" s="68"/>
@@ -5243,7 +5243,7 @@
       <c r="G24" s="68"/>
       <c r="H24" s="69"/>
       <c r="I24" s="68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J24" s="68"/>
       <c r="K24" s="68"/>
@@ -5259,7 +5259,7 @@
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J25" s="68"/>
       <c r="K25" s="68"/>
@@ -5270,7 +5270,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B26" s="77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="78"/>
       <c r="D26" s="78"/>
@@ -5282,7 +5282,7 @@
       <c r="G26" s="68"/>
       <c r="H26" s="69"/>
       <c r="I26" s="68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J26" s="68"/>
       <c r="K26" s="68"/>
@@ -5294,7 +5294,7 @@
     <row r="27" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B27" s="69"/>
       <c r="C27" s="68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="68"/>
       <c r="E27" s="68"/>
@@ -5304,7 +5304,7 @@
       <c r="G27" s="68"/>
       <c r="H27" s="69"/>
       <c r="I27" s="68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J27" s="68"/>
       <c r="K27" s="68"/>
@@ -5314,7 +5314,7 @@
     <row r="28" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B28" s="69"/>
       <c r="C28" s="68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="68"/>
       <c r="E28" s="68"/>
@@ -5322,7 +5322,7 @@
       <c r="G28" s="68"/>
       <c r="H28" s="69"/>
       <c r="I28" s="68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J28" s="68"/>
       <c r="K28" s="68"/>
@@ -5332,7 +5332,7 @@
     <row r="29" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B29" s="69"/>
       <c r="C29" s="68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29" s="68"/>
       <c r="E29" s="68"/>
@@ -5340,7 +5340,7 @@
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J29" s="68"/>
       <c r="K29" s="68"/>
@@ -5358,7 +5358,7 @@
       <c r="G30" s="68"/>
       <c r="H30" s="69"/>
       <c r="I30" s="68" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J30" s="68"/>
       <c r="K30" s="68"/>
@@ -5373,7 +5373,7 @@
       <c r="F31" s="76"/>
       <c r="G31" s="68"/>
       <c r="H31" s="69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I31" s="68"/>
       <c r="J31" s="68"/>
@@ -5385,7 +5385,7 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B32" s="74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C32" s="81"/>
       <c r="D32" s="81"/>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G32" s="68"/>
       <c r="H32" s="74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I32" s="81"/>
       <c r="J32" s="81"/>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B33" s="69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" s="68"/>
       <c r="D33" s="68"/>
@@ -5428,14 +5428,14 @@
     <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B34" s="69"/>
       <c r="C34" s="68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D34" s="68"/>
       <c r="E34" s="68"/>
       <c r="F34" s="76"/>
       <c r="G34" s="68"/>
       <c r="H34" s="69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I34" s="68"/>
       <c r="J34" s="68"/>
@@ -5446,7 +5446,7 @@
     <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B35" s="69"/>
       <c r="C35" s="68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D35" s="68"/>
       <c r="E35" s="68"/>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="G35" s="68"/>
       <c r="H35" s="69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I35" s="68"/>
       <c r="J35" s="68"/>
@@ -5468,7 +5468,7 @@
     <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36" s="69"/>
       <c r="C36" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" s="68"/>
       <c r="E36" s="68"/>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I36" s="81"/>
       <c r="J36" s="81"/>
@@ -5491,7 +5491,7 @@
     <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="69"/>
       <c r="C37" s="68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D37" s="68"/>
       <c r="E37" s="68"/>
@@ -5514,7 +5514,7 @@
       <c r="F38" s="76"/>
       <c r="G38" s="68"/>
       <c r="H38" s="69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I38" s="68"/>
       <c r="J38" s="68"/>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B39" s="69" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="68"/>
       <c r="D39" s="68"/>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I39" s="68"/>
       <c r="J39" s="68"/>
@@ -5551,7 +5551,7 @@
     <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B40" s="69"/>
       <c r="C40" s="68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D40" s="68"/>
       <c r="E40" s="68"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="G40" s="68"/>
       <c r="H40" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I40" s="81"/>
       <c r="J40" s="81"/>
@@ -5574,7 +5574,7 @@
     <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B41" s="69"/>
       <c r="C41" s="68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D41" s="68"/>
       <c r="E41" s="68"/>
@@ -5590,7 +5590,7 @@
     <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B42" s="69"/>
       <c r="C42" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D42" s="68"/>
       <c r="E42" s="68"/>
@@ -5619,7 +5619,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B44" s="86" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" s="68"/>
       <c r="D44" s="68"/>
@@ -5639,7 +5639,7 @@
     <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B45" s="69"/>
       <c r="C45" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D45" s="68"/>
       <c r="E45" s="68"/>
@@ -5657,7 +5657,7 @@
     <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B46" s="69"/>
       <c r="C46" s="68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D46" s="68"/>
       <c r="E46" s="68"/>
@@ -5689,15 +5689,15 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B50" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="67" t="s">
         <v>102</v>
-      </c>
-      <c r="C50" s="67" t="s">
-        <v>103</v>
       </c>
       <c r="F50" s="87">
         <f>F20/F33</f>
@@ -5706,7 +5706,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C51" s="67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F51" s="87">
         <f>-M35/M19</f>
@@ -5715,7 +5715,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C52" s="67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F52" s="88">
         <f>+M32/F19</f>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C53" s="67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F53" s="88">
         <f>+M40/M19</f>
@@ -5733,15 +5733,15 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B55" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="67" t="s">
         <v>107</v>
-      </c>
-      <c r="C55" s="67" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C56" s="89" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D56" s="89"/>
       <c r="E56" s="89"/>
@@ -5754,13 +5754,13 @@
       <c r="D57" s="89"/>
       <c r="E57" s="89"/>
       <c r="F57" s="90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G57" s="91" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -5772,7 +5772,7 @@
         <v>2550</v>
       </c>
       <c r="G58" s="94" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="95">
         <f>F58</f>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C60" s="89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D60" s="89"/>
       <c r="E60" s="89"/>
@@ -5802,13 +5802,13 @@
       <c r="D61" s="89"/>
       <c r="E61" s="89"/>
       <c r="F61" s="90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G61" s="91" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" s="92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -5820,7 +5820,7 @@
         <v>-40</v>
       </c>
       <c r="G62" s="94" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62" s="95">
         <f>5%*M20</f>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C64" s="89" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D64" s="89"/>
       <c r="E64" s="89"/>
@@ -5850,13 +5850,13 @@
       <c r="D65" s="89"/>
       <c r="E65" s="89"/>
       <c r="F65" s="90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G65" s="91" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65" s="92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="3:15" x14ac:dyDescent="0.2">
@@ -5867,7 +5867,7 @@
         <v>-100</v>
       </c>
       <c r="G66" s="94" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H66" s="95">
         <v>-100</v>
@@ -5891,18 +5891,18 @@
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C69" s="89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D69" s="89"/>
       <c r="E69" s="89"/>
       <c r="F69" s="90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G69" s="91" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69" s="92" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.2">
@@ -5913,7 +5913,7 @@
         <v>-600</v>
       </c>
       <c r="G70" s="94" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" s="95">
         <v>-600</v>
@@ -5930,20 +5930,20 @@
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C72" s="89" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D72" s="89"/>
       <c r="E72" s="89" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F72" s="92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G72" s="91" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" s="92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O72" s="96"/>
     </row>
@@ -5956,7 +5956,7 @@
         <v>50000</v>
       </c>
       <c r="G73" s="94" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" s="95">
         <f>+F73</f>
@@ -5975,16 +5975,16 @@
       <c r="C75" s="89"/>
       <c r="D75" s="89"/>
       <c r="E75" s="89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F75" s="92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G75" s="91" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" s="92" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="3:15" x14ac:dyDescent="0.2">
@@ -5995,7 +5995,7 @@
         <v>-500</v>
       </c>
       <c r="G76" s="94" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" s="95">
         <f>+F76</f>
@@ -6014,16 +6014,16 @@
       <c r="C78" s="89"/>
       <c r="D78" s="89"/>
       <c r="E78" s="89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F78" s="90" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G78" s="91" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="92" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="3:15" x14ac:dyDescent="0.2">
@@ -6048,26 +6048,26 @@
     </row>
     <row r="81" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B81" s="67" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B83" s="117" t="s">
+      <c r="B83" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="C83" s="111"/>
+      <c r="D83" s="111"/>
+      <c r="E83" s="111"/>
+      <c r="F83" s="111"/>
+      <c r="G83" s="68"/>
+      <c r="H83" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="C83" s="117"/>
-      <c r="D83" s="117"/>
-      <c r="E83" s="117"/>
-      <c r="F83" s="117"/>
-      <c r="G83" s="68"/>
-      <c r="H83" s="117" t="s">
-        <v>101</v>
-      </c>
-      <c r="I83" s="117"/>
-      <c r="J83" s="117"/>
-      <c r="K83" s="117"/>
-      <c r="L83" s="117"/>
-      <c r="M83" s="117"/>
+      <c r="I83" s="111"/>
+      <c r="J83" s="111"/>
+      <c r="K83" s="111"/>
+      <c r="L83" s="111"/>
+      <c r="M83" s="111"/>
     </row>
     <row r="84" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B84" s="69"/>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="85" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B85" s="71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C85" s="72"/>
       <c r="D85" s="72"/>
@@ -6093,7 +6093,7 @@
       <c r="F85" s="73"/>
       <c r="G85" s="68"/>
       <c r="H85" s="71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I85" s="72"/>
       <c r="J85" s="72"/>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="86" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B86" s="74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C86" s="68"/>
       <c r="D86" s="68"/>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I86" s="68"/>
       <c r="J86" s="68"/>
@@ -6127,7 +6127,7 @@
     </row>
     <row r="87" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B87" s="77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C87" s="78"/>
       <c r="D87" s="78"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="G87" s="68"/>
       <c r="H87" s="69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I87" s="68"/>
       <c r="J87" s="68"/>
@@ -6152,7 +6152,7 @@
     <row r="88" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B88" s="69"/>
       <c r="C88" s="68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D88" s="68"/>
       <c r="E88" s="68"/>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I88" s="81"/>
       <c r="J88" s="81"/>
@@ -6176,7 +6176,7 @@
     <row r="89" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B89" s="69"/>
       <c r="C89" s="68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D89" s="68"/>
       <c r="E89" s="68"/>
@@ -6195,14 +6195,14 @@
     <row r="90" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B90" s="69"/>
       <c r="C90" s="68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D90" s="68"/>
       <c r="E90" s="68"/>
       <c r="F90" s="76"/>
       <c r="G90" s="68"/>
       <c r="H90" s="69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I90" s="68"/>
       <c r="J90" s="68"/>
@@ -6216,7 +6216,7 @@
     <row r="91" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B91" s="69"/>
       <c r="C91" s="68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D91" s="68"/>
       <c r="E91" s="68"/>
@@ -6224,7 +6224,7 @@
       <c r="G91" s="68"/>
       <c r="H91" s="69"/>
       <c r="I91" s="68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J91" s="68"/>
       <c r="K91" s="68"/>
@@ -6243,7 +6243,7 @@
       <c r="G92" s="68"/>
       <c r="H92" s="69"/>
       <c r="I92" s="68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J92" s="68"/>
       <c r="K92" s="68"/>
@@ -6255,7 +6255,7 @@
     </row>
     <row r="93" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B93" s="77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C93" s="78"/>
       <c r="D93" s="78"/>
@@ -6267,7 +6267,7 @@
       <c r="G93" s="68"/>
       <c r="H93" s="69"/>
       <c r="I93" s="68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J93" s="68"/>
       <c r="K93" s="68"/>
@@ -6280,7 +6280,7 @@
     <row r="94" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B94" s="69"/>
       <c r="C94" s="68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D94" s="68"/>
       <c r="E94" s="68"/>
@@ -6291,7 +6291,7 @@
       <c r="G94" s="68"/>
       <c r="H94" s="69"/>
       <c r="I94" s="68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J94" s="68"/>
       <c r="K94" s="68"/>
@@ -6301,7 +6301,7 @@
     <row r="95" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B95" s="69"/>
       <c r="C95" s="68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D95" s="68"/>
       <c r="E95" s="68"/>
@@ -6309,7 +6309,7 @@
       <c r="G95" s="68"/>
       <c r="H95" s="69"/>
       <c r="I95" s="68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J95" s="68"/>
       <c r="K95" s="68"/>
@@ -6319,7 +6319,7 @@
     <row r="96" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B96" s="69"/>
       <c r="C96" s="68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D96" s="68"/>
       <c r="E96" s="68"/>
@@ -6327,7 +6327,7 @@
       <c r="G96" s="68"/>
       <c r="H96" s="69"/>
       <c r="I96" s="68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J96" s="68"/>
       <c r="K96" s="68"/>
@@ -6346,7 +6346,7 @@
       <c r="G97" s="68"/>
       <c r="H97" s="69"/>
       <c r="I97" s="68" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J97" s="68"/>
       <c r="K97" s="68"/>
@@ -6361,7 +6361,7 @@
       <c r="F98" s="76"/>
       <c r="G98" s="68"/>
       <c r="H98" s="69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I98" s="68"/>
       <c r="J98" s="68"/>
@@ -6374,7 +6374,7 @@
     </row>
     <row r="99" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B99" s="74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C99" s="81"/>
       <c r="D99" s="81"/>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="G99" s="68"/>
       <c r="H99" s="74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I99" s="81"/>
       <c r="J99" s="81"/>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="100" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B100" s="69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C100" s="68"/>
       <c r="D100" s="68"/>
@@ -6418,14 +6418,14 @@
     <row r="101" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B101" s="69"/>
       <c r="C101" s="68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D101" s="68"/>
       <c r="E101" s="68"/>
       <c r="F101" s="76"/>
       <c r="G101" s="68"/>
       <c r="H101" s="69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I101" s="68"/>
       <c r="J101" s="68"/>
@@ -6436,7 +6436,7 @@
     <row r="102" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B102" s="69"/>
       <c r="C102" s="68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D102" s="68"/>
       <c r="E102" s="68"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G102" s="68"/>
       <c r="H102" s="69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I102" s="68"/>
       <c r="J102" s="68"/>
@@ -6460,7 +6460,7 @@
     <row r="103" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B103" s="69"/>
       <c r="C103" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D103" s="68"/>
       <c r="E103" s="68"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="G103" s="68"/>
       <c r="H103" s="74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I103" s="81"/>
       <c r="J103" s="81"/>
@@ -6484,7 +6484,7 @@
     <row r="104" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B104" s="69"/>
       <c r="C104" s="68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D104" s="68"/>
       <c r="E104" s="68"/>
@@ -6508,7 +6508,7 @@
       <c r="F105" s="76"/>
       <c r="G105" s="68"/>
       <c r="H105" s="69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I105" s="68"/>
       <c r="J105" s="68"/>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="106" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B106" s="69" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C106" s="68"/>
       <c r="D106" s="68"/>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="G106" s="68"/>
       <c r="H106" s="69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I106" s="68"/>
       <c r="J106" s="68"/>
@@ -6546,7 +6546,7 @@
     <row r="107" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B107" s="69"/>
       <c r="C107" s="68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D107" s="68"/>
       <c r="E107" s="68"/>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="G107" s="68"/>
       <c r="H107" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I107" s="81"/>
       <c r="J107" s="81"/>
@@ -6570,7 +6570,7 @@
     <row r="108" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B108" s="69"/>
       <c r="C108" s="68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D108" s="68"/>
       <c r="E108" s="68"/>
@@ -6586,7 +6586,7 @@
     <row r="109" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B109" s="69"/>
       <c r="C109" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D109" s="68"/>
       <c r="E109" s="68"/>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="111" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B111" s="86" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C111" s="68"/>
       <c r="D111" s="68"/>
@@ -6635,7 +6635,7 @@
     <row r="112" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B112" s="69"/>
       <c r="C112" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D112" s="68"/>
       <c r="E112" s="68"/>
@@ -6654,7 +6654,7 @@
     <row r="113" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B113" s="69"/>
       <c r="C113" s="68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D113" s="68"/>
       <c r="E113" s="68"/>
@@ -6686,7 +6686,7 @@
     </row>
     <row r="117" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C117" s="67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F117" s="87">
         <f>F87/F100</f>
@@ -6695,7 +6695,7 @@
     </row>
     <row r="118" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C118" s="67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F118" s="87">
         <f>-M102/M86</f>
@@ -6704,7 +6704,7 @@
     </row>
     <row r="119" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C119" s="67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F119" s="88">
         <f>+M99/F86</f>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="120" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C120" s="67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F120" s="88">
         <f>+M107/M86</f>
@@ -6722,26 +6722,26 @@
     </row>
     <row r="121" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B121" s="67" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="123" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B123" s="117" t="s">
+      <c r="B123" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="C123" s="111"/>
+      <c r="D123" s="111"/>
+      <c r="E123" s="111"/>
+      <c r="F123" s="111"/>
+      <c r="G123" s="68"/>
+      <c r="H123" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="C123" s="117"/>
-      <c r="D123" s="117"/>
-      <c r="E123" s="117"/>
-      <c r="F123" s="117"/>
-      <c r="G123" s="68"/>
-      <c r="H123" s="117" t="s">
-        <v>101</v>
-      </c>
-      <c r="I123" s="117"/>
-      <c r="J123" s="117"/>
-      <c r="K123" s="117"/>
-      <c r="L123" s="117"/>
-      <c r="M123" s="117"/>
+      <c r="I123" s="111"/>
+      <c r="J123" s="111"/>
+      <c r="K123" s="111"/>
+      <c r="L123" s="111"/>
+      <c r="M123" s="111"/>
     </row>
     <row r="124" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B124" s="69"/>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="125" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B125" s="71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C125" s="72"/>
       <c r="D125" s="72"/>
@@ -6767,7 +6767,7 @@
       <c r="F125" s="73"/>
       <c r="G125" s="68"/>
       <c r="H125" s="71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I125" s="72"/>
       <c r="J125" s="72"/>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="126" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B126" s="74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C126" s="68"/>
       <c r="D126" s="68"/>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="G126" s="68"/>
       <c r="H126" s="69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I126" s="68"/>
       <c r="J126" s="68"/>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="127" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B127" s="77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C127" s="78"/>
       <c r="D127" s="78"/>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="G127" s="68"/>
       <c r="H127" s="69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I127" s="68"/>
       <c r="J127" s="68"/>
@@ -6826,7 +6826,7 @@
     <row r="128" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B128" s="69"/>
       <c r="C128" s="68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D128" s="68"/>
       <c r="E128" s="68"/>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="G128" s="68"/>
       <c r="H128" s="74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I128" s="81"/>
       <c r="J128" s="81"/>
@@ -6850,7 +6850,7 @@
     <row r="129" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B129" s="69"/>
       <c r="C129" s="68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D129" s="68"/>
       <c r="E129" s="68"/>
@@ -6869,14 +6869,14 @@
     <row r="130" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B130" s="69"/>
       <c r="C130" s="68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D130" s="68"/>
       <c r="E130" s="68"/>
       <c r="F130" s="76"/>
       <c r="G130" s="68"/>
       <c r="H130" s="69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I130" s="68"/>
       <c r="J130" s="68"/>
@@ -6890,7 +6890,7 @@
     <row r="131" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B131" s="69"/>
       <c r="C131" s="68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D131" s="68"/>
       <c r="E131" s="68"/>
@@ -6898,7 +6898,7 @@
       <c r="G131" s="68"/>
       <c r="H131" s="69"/>
       <c r="I131" s="68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J131" s="68"/>
       <c r="K131" s="68"/>
@@ -6917,7 +6917,7 @@
       <c r="G132" s="68"/>
       <c r="H132" s="69"/>
       <c r="I132" s="68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J132" s="68"/>
       <c r="K132" s="68"/>
@@ -6929,7 +6929,7 @@
     </row>
     <row r="133" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B133" s="77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C133" s="78"/>
       <c r="D133" s="78"/>
@@ -6941,7 +6941,7 @@
       <c r="G133" s="68"/>
       <c r="H133" s="69"/>
       <c r="I133" s="68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J133" s="68"/>
       <c r="K133" s="68"/>
@@ -6954,7 +6954,7 @@
     <row r="134" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B134" s="69"/>
       <c r="C134" s="68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D134" s="68"/>
       <c r="E134" s="68"/>
@@ -6965,7 +6965,7 @@
       <c r="G134" s="68"/>
       <c r="H134" s="69"/>
       <c r="I134" s="68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J134" s="68"/>
       <c r="K134" s="68"/>
@@ -6975,7 +6975,7 @@
     <row r="135" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B135" s="69"/>
       <c r="C135" s="68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D135" s="68"/>
       <c r="E135" s="68"/>
@@ -6983,7 +6983,7 @@
       <c r="G135" s="68"/>
       <c r="H135" s="69"/>
       <c r="I135" s="68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J135" s="68"/>
       <c r="K135" s="68"/>
@@ -6993,7 +6993,7 @@
     <row r="136" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B136" s="69"/>
       <c r="C136" s="68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D136" s="68"/>
       <c r="E136" s="68"/>
@@ -7001,7 +7001,7 @@
       <c r="G136" s="68"/>
       <c r="H136" s="69"/>
       <c r="I136" s="68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J136" s="68"/>
       <c r="K136" s="68"/>
@@ -7020,7 +7020,7 @@
       <c r="G137" s="68"/>
       <c r="H137" s="69"/>
       <c r="I137" s="68" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J137" s="68"/>
       <c r="K137" s="68"/>
@@ -7035,7 +7035,7 @@
       <c r="F138" s="76"/>
       <c r="G138" s="68"/>
       <c r="H138" s="69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I138" s="68"/>
       <c r="J138" s="68"/>
@@ -7048,7 +7048,7 @@
     </row>
     <row r="139" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B139" s="74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C139" s="81"/>
       <c r="D139" s="81"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G139" s="68"/>
       <c r="H139" s="74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I139" s="81"/>
       <c r="J139" s="81"/>
@@ -7072,7 +7072,7 @@
     </row>
     <row r="140" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B140" s="69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C140" s="68"/>
       <c r="D140" s="68"/>
@@ -7092,14 +7092,14 @@
     <row r="141" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B141" s="69"/>
       <c r="C141" s="68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D141" s="68"/>
       <c r="E141" s="68"/>
       <c r="F141" s="76"/>
       <c r="G141" s="68"/>
       <c r="H141" s="69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I141" s="68"/>
       <c r="J141" s="68"/>
@@ -7110,7 +7110,7 @@
     <row r="142" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B142" s="69"/>
       <c r="C142" s="68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D142" s="68"/>
       <c r="E142" s="68"/>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="G142" s="68"/>
       <c r="H142" s="69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I142" s="68"/>
       <c r="J142" s="68"/>
@@ -7134,7 +7134,7 @@
     <row r="143" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B143" s="69"/>
       <c r="C143" s="68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D143" s="68"/>
       <c r="E143" s="68"/>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G143" s="68"/>
       <c r="H143" s="74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I143" s="81"/>
       <c r="J143" s="81"/>
@@ -7158,7 +7158,7 @@
     <row r="144" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B144" s="69"/>
       <c r="C144" s="68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D144" s="68"/>
       <c r="E144" s="68"/>
@@ -7182,7 +7182,7 @@
       <c r="F145" s="76"/>
       <c r="G145" s="68"/>
       <c r="H145" s="69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I145" s="68"/>
       <c r="J145" s="68"/>
@@ -7195,7 +7195,7 @@
     </row>
     <row r="146" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B146" s="69" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C146" s="68"/>
       <c r="D146" s="68"/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="G146" s="68"/>
       <c r="H146" s="69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I146" s="68"/>
       <c r="J146" s="68"/>
@@ -7220,7 +7220,7 @@
     <row r="147" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B147" s="69"/>
       <c r="C147" s="68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D147" s="68"/>
       <c r="E147" s="68"/>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="G147" s="68"/>
       <c r="H147" s="74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I147" s="81"/>
       <c r="J147" s="81"/>
@@ -7244,7 +7244,7 @@
     <row r="148" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B148" s="69"/>
       <c r="C148" s="68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D148" s="68"/>
       <c r="E148" s="68"/>
@@ -7260,7 +7260,7 @@
     <row r="149" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B149" s="69"/>
       <c r="C149" s="68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D149" s="68"/>
       <c r="E149" s="68"/>
@@ -7289,7 +7289,7 @@
     </row>
     <row r="151" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B151" s="86" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C151" s="68"/>
       <c r="D151" s="68"/>
@@ -7309,7 +7309,7 @@
     <row r="152" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B152" s="69"/>
       <c r="C152" s="68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D152" s="68"/>
       <c r="E152" s="68"/>
@@ -7328,7 +7328,7 @@
     <row r="153" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B153" s="69"/>
       <c r="C153" s="68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D153" s="68"/>
       <c r="E153" s="68"/>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="157" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C157" s="67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F157" s="87">
         <f>F127/F140</f>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="158" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C158" s="67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F158" s="87">
         <f>-M142/M126</f>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="159" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C159" s="67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F159" s="104">
         <f>+M139/F126</f>
@@ -7387,7 +7387,7 @@
     </row>
     <row r="160" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C160" s="67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F160" s="88">
         <f>+M147/M126</f>
@@ -7402,21 +7402,21 @@
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B163" s="105" t="s">
+        <v>119</v>
+      </c>
+      <c r="C163" s="106" t="s">
         <v>120</v>
       </c>
-      <c r="C163" s="106" t="s">
+      <c r="D163" s="106" t="s">
+        <v>43</v>
+      </c>
+      <c r="E163" s="106" t="s">
         <v>121</v>
-      </c>
-      <c r="D163" s="106" t="s">
-        <v>44</v>
-      </c>
-      <c r="E163" s="106" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B164" s="67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C164" s="107">
         <f>+F50</f>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B165" s="67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C165" s="107">
         <f>+F51*100</f>
@@ -7450,7 +7450,7 @@
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B166" s="67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C166" s="108">
         <f>+F52</f>
@@ -7467,7 +7467,7 @@
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B167" s="105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C167" s="109">
         <f>+F53</f>
@@ -7484,7 +7484,7 @@
     </row>
     <row r="183" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C183" s="67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
